--- a/sample-data/company-budget-pack.xlsx
+++ b/sample-data/company-budget-pack.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="54">
   <si>
     <t>Northwind Manufacturing A.Ş.</t>
   </si>
@@ -121,6 +121,39 @@
   </si>
   <si>
     <t>ARA TOPLAM — OPERATING</t>
+  </si>
+  <si>
+    <t>GENEL YÖNETİM GİDERLERİ</t>
+  </si>
+  <si>
+    <t>770</t>
+  </si>
+  <si>
+    <t>Genel Yönetim Giderleri</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>770.01</t>
+  </si>
+  <si>
+    <t>Personel Giderleri</t>
+  </si>
+  <si>
+    <t>770.02</t>
+  </si>
+  <si>
+    <t>Kira Giderleri</t>
+  </si>
+  <si>
+    <t>770.03</t>
+  </si>
+  <si>
+    <t>Kırtasiye Giderleri</t>
+  </si>
+  <si>
+    <t>TOPLAM — GENEL YÖNETİM</t>
   </si>
   <si>
     <t>OTHER</t>
@@ -553,7 +586,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -914,63 +947,210 @@
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>39</v>
+      </c>
+      <c r="D19">
+        <v>100000</v>
+      </c>
+      <c r="E19">
+        <v>100000</v>
       </c>
       <c r="F19">
-        <v>3000</v>
+        <v>103000</v>
       </c>
       <c r="G19">
-        <v>3000</v>
+        <v>103000</v>
       </c>
       <c r="H19">
-        <v>3200</v>
+        <v>105000</v>
       </c>
       <c r="I19">
-        <v>3200</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
         <v>39</v>
       </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D20">
+        <v>70000</v>
+      </c>
+      <c r="E20">
+        <v>70000</v>
+      </c>
+      <c r="F20">
+        <v>72000</v>
+      </c>
+      <c r="G20">
+        <v>72000</v>
+      </c>
+      <c r="H20">
+        <v>73000</v>
+      </c>
+      <c r="I20">
+        <v>73000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21">
+        <v>20000</v>
+      </c>
+      <c r="E21">
+        <v>20000</v>
+      </c>
+      <c r="F21">
+        <v>21000</v>
+      </c>
+      <c r="G21">
+        <v>21000</v>
+      </c>
+      <c r="H21">
+        <v>22000</v>
+      </c>
+      <c r="I21">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22">
+        <v>10000</v>
+      </c>
+      <c r="E22">
+        <v>10000</v>
+      </c>
+      <c r="F22">
+        <v>10000</v>
+      </c>
+      <c r="G22">
+        <v>10000</v>
+      </c>
+      <c r="H22">
+        <v>10000</v>
+      </c>
+      <c r="I22">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2">
+        <v>100000</v>
+      </c>
+      <c r="E23" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F23" s="2">
+        <v>103000</v>
+      </c>
+      <c r="G23" s="2">
+        <v>103000</v>
+      </c>
+      <c r="H23" s="2">
+        <v>105000</v>
+      </c>
+      <c r="I23" s="2">
+        <v>105000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25">
+        <v>3000</v>
+      </c>
+      <c r="G25">
+        <v>3000</v>
+      </c>
+      <c r="H25">
+        <v>3200</v>
+      </c>
+      <c r="I25">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" t="s">
         <v>17</v>
       </c>
-      <c r="D20">
+      <c r="D26">
         <v>4000</v>
       </c>
-      <c r="E20">
+      <c r="E26">
         <v>4200</v>
       </c>
-      <c r="F20">
+      <c r="F26">
         <v>4000</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2">
+    <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2">
         <v>4000</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E27" s="2">
         <v>4200</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F27" s="2">
         <v>7000</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G27" s="2">
         <v>3000</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H27" s="2">
         <v>3200</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I27" s="2">
         <v>3200</v>
       </c>
     </row>
@@ -982,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -998,7 +1178,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -1343,63 +1523,210 @@
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>39</v>
+      </c>
+      <c r="D19">
+        <v>98000</v>
+      </c>
+      <c r="E19">
+        <v>104000</v>
       </c>
       <c r="F19">
-        <v>3000</v>
+        <v>101500</v>
       </c>
       <c r="G19">
-        <v>3200</v>
+        <v>109000</v>
       </c>
       <c r="H19">
-        <v>3500</v>
+        <v>106000</v>
       </c>
       <c r="I19">
-        <v>3400</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
         <v>39</v>
       </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D20">
+        <v>69000</v>
+      </c>
+      <c r="E20">
+        <v>73000</v>
+      </c>
+      <c r="F20">
+        <v>71000</v>
+      </c>
+      <c r="G20">
+        <v>75000</v>
+      </c>
+      <c r="H20">
+        <v>74000</v>
+      </c>
+      <c r="I20">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21">
+        <v>20000</v>
+      </c>
+      <c r="E21">
+        <v>21000</v>
+      </c>
+      <c r="F21">
+        <v>21000</v>
+      </c>
+      <c r="G21">
+        <v>23000</v>
+      </c>
+      <c r="H21">
+        <v>22000</v>
+      </c>
+      <c r="I21">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22">
+        <v>9000</v>
+      </c>
+      <c r="E22">
+        <v>10000</v>
+      </c>
+      <c r="F22">
+        <v>9500</v>
+      </c>
+      <c r="G22">
+        <v>11000</v>
+      </c>
+      <c r="H22">
+        <v>10000</v>
+      </c>
+      <c r="I22">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2">
+        <v>98000</v>
+      </c>
+      <c r="E23" s="2">
+        <v>104000</v>
+      </c>
+      <c r="F23" s="2">
+        <v>101500</v>
+      </c>
+      <c r="G23" s="2">
+        <v>109000</v>
+      </c>
+      <c r="H23" s="2">
+        <v>106000</v>
+      </c>
+      <c r="I23" s="2">
+        <v>104000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25">
+        <v>3000</v>
+      </c>
+      <c r="G25">
+        <v>3200</v>
+      </c>
+      <c r="H25">
+        <v>3500</v>
+      </c>
+      <c r="I25">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" t="s">
         <v>17</v>
       </c>
-      <c r="D20">
+      <c r="D26">
         <v>4100</v>
       </c>
-      <c r="E20">
+      <c r="E26">
         <v>4000</v>
       </c>
-      <c r="F20">
+      <c r="F26">
         <v>3800</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2">
+    <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2">
         <v>4100</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E27" s="2">
         <v>4000</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F27" s="2">
         <v>6800</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G27" s="2">
         <v>3200</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H27" s="2">
         <v>3500</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I27" s="2">
         <v>3400</v>
       </c>
     </row>
